--- a/out/LSTM-Mamba1_repeat_3_000008.xlsx
+++ b/out/LSTM-Mamba1_repeat_3_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.242781613595273</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001405772226231638</v>
+        <v>-9.028927320521324e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1614962284495334</v>
+        <v>-0.1037250332593648</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1617709512806789</v>
+        <v>-0.1038953169789104</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4823568010975823</v>
+        <v>0.2876418110555966</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8038693081147796</v>
+        <v>0.4719405879425919</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03436782080453595</v>
+        <v>0.02049438205934407</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3894739543912082</v>
+        <v>0.2248262053035155</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06026944784898779</v>
+        <v>0.03594029158310495</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4756337436872439</v>
+        <v>0.2762054937622342</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.07322057315774763</v>
+        <v>0.04366320975871988</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5617994508200237</v>
+        <v>0.3275882019587611</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01937583320039024</v>
+        <v>0.01155418788124789</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5272373911593266</v>
+        <v>0.3069779783840266</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01076454431467968</v>
+        <v>0.006417104351165654</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5293719564027936</v>
+        <v>0.3082488606887963</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02261743727044311</v>
+        <v>0.01348698945083388</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5638560696587405</v>
+        <v>0.3288123602160108</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008883069328844096</v>
+        <v>0.005294658180000239</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.55898458273166</v>
+        <v>0.3259053062485033</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006323787010950994</v>
+        <v>0.003769158075759273</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5627471101080258</v>
+        <v>0.3281472705010839</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002486730349881667</v>
+        <v>0.001480532971537081</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5613901319556849</v>
+        <v>0.3273358735346063</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001408475874147683</v>
+        <v>0.0008381530023541796</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5617204438282386</v>
+        <v>0.3275309646785506</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005340354768829103</v>
+        <v>0.0003167771692067918</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.561377366302291</v>
+        <v>0.3273241493362637</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002471199415423035</v>
+        <v>0.0001458315807480156</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.561338288989516</v>
+        <v>0.3272988064421003</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.784240885070706e-05</v>
+        <v>4.989812001607026e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5612655404891004</v>
+        <v>0.3272534524713112</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.218818784456313e-05</v>
+        <v>1.121751555640607e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5612224633554674</v>
+        <v>0.3272256063400598</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>8.832586798111064e-06</v>
+        <v>3.108757778203038e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5612174417608481</v>
+        <v>0.3272205936811452</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.191662034084867e-06</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5612134964247478</v>
+        <v>0.3272162480553358</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5612112454970163</v>
+        <v>0.3272128977005431</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5612056538370079</v>
+        <v>0.3272075283735553</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.561199329843</v>
+        <v>0.3272015356401249</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5611939620544216</v>
+        <v>0.3271961678515465</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5611939988029133</v>
+        <v>0.3271962046000382</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5611941090483888</v>
+        <v>0.3271963148455138</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5611941825453726</v>
+        <v>0.3271963883424974</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5611943662878317</v>
+        <v>0.3271965720849566</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5611959097244882</v>
+        <v>0.327198115521613</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5611973796641613</v>
+        <v>0.3271995854612861</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5611986291128832</v>
+        <v>0.3272008349100081</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5611999888070806</v>
+        <v>0.3272021946042054</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5611977838975712</v>
+        <v>0.3271999896946962</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5611973796641613</v>
+        <v>0.3271995854612861</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5611965344488493</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5611970856762265</v>
+        <v>0.3271992914733514</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5611967549398001</v>
+        <v>0.327198960736925</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5611964609518657</v>
+        <v>0.3271986667489906</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5611965344488493</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5611960934669473</v>
+        <v>0.3271982992640722</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5611959832214718</v>
+        <v>0.3271981890185967</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5611959464729801</v>
+        <v>0.327198152270105</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5611960934669473</v>
+        <v>0.3271982992640722</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5611956157365536</v>
+        <v>0.3271978215336785</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.561196571197341</v>
+        <v>0.3271987769944659</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5611965344488493</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5611962037124228</v>
+        <v>0.3271984095095478</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5611966446943248</v>
+        <v>0.3271988504914497</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5611960199699637</v>
+        <v>0.3271982257670886</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5611958362275046</v>
+        <v>0.3271980420246294</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5611954319940945</v>
+        <v>0.3271976377912194</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5611945867787825</v>
+        <v>0.3271967925759074</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5611945500302908</v>
+        <v>0.3271967558274158</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5611946970242581</v>
+        <v>0.327196902821383</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5611946235272744</v>
+        <v>0.3271968293243994</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5611946970242581</v>
+        <v>0.327196902821383</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.56119473377275</v>
+        <v>0.3271969395698749</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5611946235272744</v>
+        <v>0.3271968293243994</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5611950645091764</v>
+        <v>0.3271972703063013</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5611949542637009</v>
+        <v>0.3271971600608258</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5611949175152089</v>
+        <v>0.3271971233123338</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5611948440182253</v>
+        <v>0.3271970498153502</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5611948072697336</v>
+        <v>0.3271970130668585</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5611945867787825</v>
+        <v>0.3271967925759074</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5611945132817989</v>
+        <v>0.3271967190789238</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5611944397848153</v>
+        <v>0.3271966455819402</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5611944765333072</v>
+        <v>0.3271966823304321</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5611943662878317</v>
+        <v>0.3271965720849566</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5611944765333072</v>
+        <v>0.3271966823304321</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5611947705212417</v>
+        <v>0.3271969763183666</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_3_000008.xlsx
+++ b/out/LSTM-Mamba1_repeat_3_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.2042036800513534</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.778954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001405772226231638</v>
+        <v>-0.0001316043501363602</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1614962284495334</v>
+        <v>-0.1511881213613452</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1513197257114815</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.778954327415217</v>
+        <v>0.6948861808537512</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1513197257114815</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353367</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1513197257114815</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1513197257114815</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1513197257114815</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1513197257114815</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1513197257114815</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1513197257114815</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1513197257114815</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1513197257114815</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1513197257114815</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1513197257114815</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.2042036800513533</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1616368056721565</v>
+        <v>-0.1513197257114815</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.378954327415217</v>
+        <v>0.2042036800513534</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1617709512806789</v>
+        <v>-0.1514089653301651</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4823568010975823</v>
+        <v>0.3208853453011686</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.2042036800513534</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8038693081147796</v>
+        <v>0.4909778368855689</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03436782080453595</v>
+        <v>0.0228629768946642</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.4864788207510444</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3894739543912082</v>
+        <v>0.2153037833937712</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06026944784898779</v>
+        <v>0.04009399989398706</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4864788207510444</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4756337436872439</v>
+        <v>0.272621103183836</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.07322057315774763</v>
+        <v>0.04870916302084926</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5617994508200237</v>
+        <v>0.3299422385149046</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01937583320039024</v>
+        <v>0.01288982996606441</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5272373911593266</v>
+        <v>0.3069499223527331</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01076454431467968</v>
+        <v>0.007159287561814503</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5293719564027936</v>
+        <v>0.308368250276489</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02261743727044311</v>
+        <v>0.01504535816268046</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5638560696587405</v>
+        <v>0.3313086544224147</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008883069328844096</v>
+        <v>0.005907461433903376</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.55898458273166</v>
+        <v>0.328066072128827</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006323787010950994</v>
+        <v>0.004205566664958129</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5627471101080258</v>
+        <v>0.3305677949704134</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002486730349881667</v>
+        <v>0.001652985153790471</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5613901319556849</v>
+        <v>0.3296631953388012</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001408475874147683</v>
+        <v>0.0009352620318757762</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5617204438282386</v>
+        <v>0.3298813105527519</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005340354768829103</v>
+        <v>0.0003531826153579251</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.561377366302291</v>
+        <v>0.3296512946028793</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002471199415423035</v>
+        <v>0.0001634469478426743</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.561338288989516</v>
+        <v>0.3296235758962592</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.784240885070706e-05</v>
+        <v>5.635672237090206e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5612655404891004</v>
+        <v>0.3295735089863108</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.218818784456313e-05</v>
+        <v>1.312545856304208e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5612224633554674</v>
+        <v>0.32954301398508</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>8.832586798111064e-06</v>
+        <v>4.062729281521043e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5612174417608481</v>
+        <v>0.3295379998368809</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.191662034084867e-06</v>
+        <v>1.369014529177619e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5612134964247478</v>
+        <v>0.3295337269193153</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5612112454970163</v>
+        <v>0.3295305592977505</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5612056538370079</v>
+        <v>0.3295251899707627</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.561199329843</v>
+        <v>0.3295191972373324</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5611939620544216</v>
+        <v>0.329513829448754</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5611939988029133</v>
+        <v>0.3295138661972457</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5611941090483888</v>
+        <v>0.3295139764427212</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5611941825453726</v>
+        <v>0.3295140499397048</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.2042036800513533</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5611943662878317</v>
+        <v>0.329514233682164</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5611959097244882</v>
+        <v>0.3295157771188205</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5611973796641613</v>
+        <v>0.3295172470584936</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5611986291128832</v>
+        <v>0.3295184965072155</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537512</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5611999888070806</v>
+        <v>0.3295198562014128</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.2042036800513533</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5611977838975712</v>
+        <v>0.3295176512919036</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5611973796641613</v>
+        <v>0.3295172470584936</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5611965344488493</v>
+        <v>0.3295164018431816</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5611970856762265</v>
+        <v>0.3295169530705588</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5611967549398001</v>
+        <v>0.3295166223341324</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5611964609518657</v>
+        <v>0.329516328346198</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5611965344488493</v>
+        <v>0.3295164018431816</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5611960934669473</v>
+        <v>0.3295159608612797</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5611959832214718</v>
+        <v>0.3295158506158041</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5611959464729801</v>
+        <v>0.3295158138673124</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5611960934669473</v>
+        <v>0.3295159608612797</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5611956157365536</v>
+        <v>0.329515483130886</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.561196571197341</v>
+        <v>0.3295164385916733</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5611965344488493</v>
+        <v>0.3295164018431816</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5611962037124228</v>
+        <v>0.3295160711067552</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5611966446943248</v>
+        <v>0.3295165120886571</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5611960199699637</v>
+        <v>0.329515887364296</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5611958362275046</v>
+        <v>0.3295157036218369</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5611954319940945</v>
+        <v>0.3295152993884268</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5611945867787825</v>
+        <v>0.3295144541731149</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5611945500302908</v>
+        <v>0.3295144174246232</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5611946970242581</v>
+        <v>0.3295145644185904</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5611946235272744</v>
+        <v>0.3295144909216068</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5611946970242581</v>
+        <v>0.3295145644185904</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.56119473377275</v>
+        <v>0.3295146011670823</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5611946235272744</v>
+        <v>0.3295144909216068</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5611950645091764</v>
+        <v>0.3295149319035087</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5611949542637009</v>
+        <v>0.3295148216580332</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5611949175152089</v>
+        <v>0.3295147849095413</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5611948440182253</v>
+        <v>0.3295147114125576</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5611948072697336</v>
+        <v>0.3295146746640659</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5611945867787825</v>
+        <v>0.3295144541731149</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5611945132817989</v>
+        <v>0.3295143806761312</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5611944397848153</v>
+        <v>0.3295143071791476</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5611944765333072</v>
+        <v>0.3295143439276396</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5611943662878317</v>
+        <v>0.329514233682164</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5611944765333072</v>
+        <v>0.3295143439276396</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5611947705212417</v>
+        <v>0.329514637915574</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_3_000008.xlsx
+++ b/out/LSTM-Mamba1_repeat_3_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.02258915454149246</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.01253714226186275</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.005963705480098724</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.001976974308490753</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.16</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.001205790787935257</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.001492355018854141</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.001571279019117355</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.001607611775398254</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.001251332461833954</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.0009852051734924316</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.0005069561302661896</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0001186318695545197</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.2042036800513534</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.0001651979982852936</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0003633797168731689</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.585568681656149</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.0009496957063674927</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.585568681656149</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.0007631555199623108</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.585568681656149</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.0003670156002044678</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.585568681656149</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.0001701377332210541</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.585568681656149</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.0001826807856559753</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.585568681656149</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.0003236532211303711</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.585568681656149</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.0004727505147457123</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.585568681656149</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.0007015690207481384</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.585568681656149</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.0008811876177787781</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.385568681656149</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.001213151961565018</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.385568681656149</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.001297645270824432</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.385568681656149</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.00129476934671402</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.385568681656149</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.001247186213731766</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.385568681656149</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.00132153183221817</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.385568681656149</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.001505691558122635</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.385568681656149</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.001734964549541473</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.385568681656149</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.002799395471811295</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.385568681656149</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.00240812823176384</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.385568681656149</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.001878760755062103</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.385568681656149</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.001526318490505219</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.385568681656149</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.001160003244876862</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.001190397888422012</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.16</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.001079991459846497</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.3</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.001010540872812271</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.16</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.001372881233692169</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.001772910356521606</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.385568681656149</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.001828286796808243</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.385568681656149</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.002095680683851242</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.385568681656149</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.002834506332874298</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.385568681656149</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.00316990539431572</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.385568681656149</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001316043501363602</v>
+        <v>-0.0001132297395697096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1511881213613452</v>
+        <v>-0.1300792229893992</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.00133957713842392</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1513197257114815</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.0001111775636672974</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.6948861808537512</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1513197257114815</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.001299042254686356</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.004203680051353367</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1513197257114815</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.001927576959133148</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1513197257114815</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.002174936234951019</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1513197257114815</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.002069123089313507</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1513197257114815</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.001786321401596069</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1513197257114815</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.001205824315547943</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1513197257114815</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.0008348450064659119</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1513197257114815</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.0005669891834259033</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1513197257114815</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.0004634745419025421</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1513197257114815</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.0004505515098571777</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1513197257114815</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.0002971701323986053</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.2042036800513533</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1513197257114815</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.0003835521638393402</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.2042036800513534</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1514089653301651</v>
+        <v>-0.1302574926734896</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3208853453011686</v>
+        <v>0.2338688282598552</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-8.782371878623962e-05</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.2042036800513534</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4909778368855689</v>
+        <v>0.3379292005604627</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0228629768946642</v>
+        <v>0.01666306832510367</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0005373135209083557</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.4864788207510444</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2153037833937712</v>
+        <v>0.1370114310152538</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04009399989398706</v>
+        <v>0.02922147270272843</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.0005051754415035248</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4864788207510444</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.272621103183836</v>
+        <v>0.1787856740458205</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.04870916302084926</v>
+        <v>0.03550063830527529</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.001210607588291168</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3299422385149046</v>
+        <v>0.220562697515015</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01288982996606441</v>
+        <v>0.009393237161945765</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.002206366509199142</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3069499223527331</v>
+        <v>0.2038044951955106</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007159287561814503</v>
+        <v>0.005216697299636718</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.001311827450990677</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.308368250276489</v>
+        <v>0.2048368622222175</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01504535816268046</v>
+        <v>0.01096369609643938</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.0006505176424980164</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3313086544224147</v>
+        <v>0.2215547841622636</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.005907461433903376</v>
+        <v>0.004303999955310981</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.001040350645780563</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.328066072128827</v>
+        <v>0.2191901455519372</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004205566664958129</v>
+        <v>0.003063659605473376</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.002297889441251755</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3305677949704134</v>
+        <v>0.2210121838641879</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001652985153790471</v>
+        <v>0.001203523166972579</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.003112610429525375</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3296631953388012</v>
+        <v>0.2203514560409817</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0009352620318757762</v>
+        <v>0.0006809288593192138</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.004110444337129593</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3298813105527519</v>
+        <v>0.220509086376742</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003531826153579251</v>
+        <v>0.0002557099692113423</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.004924226552248001</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3296512946028793</v>
+        <v>0.2203402042714309</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001634469478426743</v>
+        <v>0.0001172066092191951</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.005471166223287582</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3296235758962592</v>
+        <v>0.2203186485755267</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>5.635672237090206e-05</v>
+        <v>4.021021648382256e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.005590938031673431</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3295735089863108</v>
+        <v>0.220280658001411</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.312545856304208e-05</v>
+        <v>8.355601046452064e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.005279053002595901</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.32954301398508</v>
+        <v>0.2202571159115553</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>4.062729281521043e-06</v>
+        <v>1.677800523226032e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.0048195980489254</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3295379998368809</v>
+        <v>0.2202521054865667</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.369014529177619e-07</v>
+        <v>-1.404168982957566e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.004022374749183655</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3295337269193153</v>
+        <v>0.2202476144442705</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.513939432721747e-06</v>
+        <v>-2.908363659633048e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.003694966435432434</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3295305592977505</v>
+        <v>0.2202438976137908</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.003553267568349838</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3295251899707627</v>
+        <v>0.2202386017837867</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.003509145230054855</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3295191972373324</v>
+        <v>0.220232939786783</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-4.890058184668745e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.003231678158044815</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.329513829448754</v>
+        <v>0.2202327560443238</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.002952005714178085</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3295138661972457</v>
+        <v>0.2202327927928155</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.002529922872781754</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3295139764427212</v>
+        <v>0.220232903038291</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.002323213964700699</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3295140499397048</v>
+        <v>0.2202329765352747</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.00139886885881424</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.2042036800513533</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.329514233682164</v>
+        <v>0.2202331602777338</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.0002542063593864441</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3295157771188205</v>
+        <v>0.2202347037143903</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.000657200813293457</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.585568681656149</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3295172470584936</v>
+        <v>0.2202361736540634</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.0008822642266750336</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.585568681656149</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3295184965072155</v>
+        <v>0.2202374231027854</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.003270011395215988</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.8948861808537512</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3295198562014128</v>
+        <v>0.2202387827969827</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.0001868419349193573</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.2042036800513533</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3295176512919036</v>
+        <v>0.2202365778874734</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.003474690020084381</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3295172470584936</v>
+        <v>0.2202361736540634</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.006019417196512222</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3295164018431816</v>
+        <v>0.2202353284387514</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.007879516109824181</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3295169530705588</v>
+        <v>0.2202358796661286</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.008970685303211212</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3295166223341324</v>
+        <v>0.2202355489297023</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.008986085653305054</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.329516328346198</v>
+        <v>0.2202352549417678</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.009042512625455856</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3295164018431816</v>
+        <v>0.2202353284387514</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.008819015696644783</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3295159608612797</v>
+        <v>0.2202348874568494</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.008436013013124466</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3295158506158041</v>
+        <v>0.2202347772113739</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.007635224610567093</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3295158138673124</v>
+        <v>0.2202347404628822</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.007285095751285553</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3295159608612797</v>
+        <v>0.2202348874568494</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.005456250160932541</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.329515483130886</v>
+        <v>0.2202344097264558</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.003832016140222549</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3295164385916733</v>
+        <v>0.2202353651872431</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.004830721765756607</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3295164018431816</v>
+        <v>0.2202353284387514</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.005906902253627777</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3295160711067552</v>
+        <v>0.220234997702325</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.006622299551963806</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3295165120886571</v>
+        <v>0.220235438684227</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.007288359105587006</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.329515887364296</v>
+        <v>0.2202348139598658</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.007505621761083603</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3295157036218369</v>
+        <v>0.2202346302174067</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.007743678987026215</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3295152993884268</v>
+        <v>0.2202342259839966</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.007695514708757401</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3295144541731149</v>
+        <v>0.2202333807686847</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.007014527916908264</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3295144174246232</v>
+        <v>0.220233344020193</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.006223130971193314</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3295145644185904</v>
+        <v>0.2202334910141602</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.005456633865833282</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3295144909216068</v>
+        <v>0.2202334175171766</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.003996778279542923</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3295145644185904</v>
+        <v>0.2202334910141602</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.004025898873806</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3295146011670823</v>
+        <v>0.2202335277626521</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.003510620445013046</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3295144909216068</v>
+        <v>0.2202334175171766</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.003678008913993835</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3295149319035087</v>
+        <v>0.2202338584990785</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.003714520484209061</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3295148216580332</v>
+        <v>0.220233748253603</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.00398530438542366</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3295147849095413</v>
+        <v>0.2202337115051111</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.00407332181930542</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3295147114125576</v>
+        <v>0.2202336380081275</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.004135269671678543</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3295146746640659</v>
+        <v>0.2202336012596358</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.004242133349180222</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.16</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3295144541731149</v>
+        <v>0.2202333807686847</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003887441009283066</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3295143806761312</v>
+        <v>0.220233307271701</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.003688827157020569</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3295143071791476</v>
+        <v>0.2202332337747174</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.003532383590936661</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3295143439276396</v>
+        <v>0.2202332705232093</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.003129877150058746</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.329514233682164</v>
+        <v>0.2202331602777338</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.002277813851833344</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3295143439276396</v>
+        <v>0.2202332705232093</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.00183810293674469</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.329514637915574</v>
+        <v>0.2202335645111438</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_3_000008.xlsx
+++ b/out/LSTM-Mamba1_repeat_3_000008.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.02258915454149246</v>
+        <v>-0.02258917130529881</v>
       </c>
       <c r="JB2" t="n">
         <v>-1.28</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.01253714226186275</v>
+        <v>-0.01253718696534634</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.8599999999999997</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.005963705480098724</v>
+        <v>-0.005963753908872604</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.4399999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.001976974308490753</v>
+        <v>-0.001977019011974335</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.16</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.001205790787935257</v>
+        <v>-0.001205865293741226</v>
       </c>
       <c r="JB6" t="n">
         <v>0.7199999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.001492355018854141</v>
+        <v>-0.001492410898208618</v>
       </c>
       <c r="JB7" t="n">
         <v>0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.001571279019117355</v>
+        <v>-0.001571431756019592</v>
       </c>
       <c r="JB8" t="n">
         <v>0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.001607611775398254</v>
+        <v>-0.00160771980881691</v>
       </c>
       <c r="JB9" t="n">
         <v>0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.001251332461833954</v>
+        <v>-0.001251425594091415</v>
       </c>
       <c r="JB10" t="n">
         <v>0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.0009852051734924316</v>
+        <v>-0.0009852498769760132</v>
       </c>
       <c r="JB11" t="n">
         <v>0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.0005069561302661896</v>
+        <v>-0.0005069486796855927</v>
       </c>
       <c r="JB12" t="n">
         <v>0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.0001186318695545197</v>
+        <v>-0.0001186132431030273</v>
       </c>
       <c r="JB13" t="n">
         <v>0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.0001651979982852936</v>
+        <v>0.000165209174156189</v>
       </c>
       <c r="JB14" t="n">
         <v>0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.0003633797168731689</v>
+        <v>0.0003634467720985413</v>
       </c>
       <c r="JB15" t="n">
         <v>0.9999999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.0009496957063674927</v>
+        <v>0.0009496845304965973</v>
       </c>
       <c r="JB16" t="n">
         <v>0.3999999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.0007631555199623108</v>
+        <v>0.0007631778717041016</v>
       </c>
       <c r="JB17" t="n">
         <v>0.3999999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.0003670156002044678</v>
+        <v>0.000366993248462677</v>
       </c>
       <c r="JB18" t="n">
         <v>0.2599999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.0001701377332210541</v>
+        <v>0.0001700706779956818</v>
       </c>
       <c r="JB19" t="n">
         <v>0.1199999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.0001826807856559753</v>
+        <v>0.0001826882362365723</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.02000000000000007</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.0003236532211303711</v>
+        <v>0.0003236271440982819</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.02000000000000007</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.0004727505147457123</v>
+        <v>0.0004727430641651154</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.02000000000000007</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.0007015690207481384</v>
+        <v>0.0007015541195869446</v>
       </c>
       <c r="JB23" t="n">
         <v>0.1199999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.0008811876177787781</v>
+        <v>0.0008811354637145996</v>
       </c>
       <c r="JB24" t="n">
         <v>0.2599999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.001213151961565018</v>
+        <v>0.001213021576404572</v>
       </c>
       <c r="JB25" t="n">
         <v>0.9999999999999998</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.001297645270824432</v>
+        <v>0.001297533512115479</v>
       </c>
       <c r="JB26" t="n">
         <v>0.9999999999999998</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.00129476934671402</v>
+        <v>0.001294732093811035</v>
       </c>
       <c r="JB27" t="n">
         <v>0.9999999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.001247186213731766</v>
+        <v>0.001247130334377289</v>
       </c>
       <c r="JB28" t="n">
         <v>0.9999999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.00132153183221817</v>
+        <v>0.001321472227573395</v>
       </c>
       <c r="JB29" t="n">
         <v>0.9999999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.001505691558122635</v>
+        <v>0.001505602151155472</v>
       </c>
       <c r="JB30" t="n">
         <v>0.9999999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.001734964549541473</v>
+        <v>0.001735039055347443</v>
       </c>
       <c r="JB31" t="n">
         <v>0.9999999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.002799395471811295</v>
+        <v>0.002799365669488907</v>
       </c>
       <c r="JB32" t="n">
         <v>0.9999999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.00240812823176384</v>
+        <v>0.002408120781183243</v>
       </c>
       <c r="JB33" t="n">
         <v>0.9999999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.001878760755062103</v>
+        <v>0.001878712326288223</v>
       </c>
       <c r="JB34" t="n">
         <v>0.2599999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.001526318490505219</v>
+        <v>0.001526251435279846</v>
       </c>
       <c r="JB35" t="n">
         <v>0.1199999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.001160003244876862</v>
+        <v>0.001159973442554474</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.02000000000000007</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.001190397888422012</v>
+        <v>0.00119033083319664</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.16</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.001079991459846497</v>
+        <v>0.00107995793223381</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.3</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.001372881233692169</v>
+        <v>0.001372914761304855</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.02000000000000007</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.001772910356521606</v>
+        <v>0.001772865653038025</v>
       </c>
       <c r="JB41" t="n">
         <v>0.1199999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.002095680683851242</v>
+        <v>0.002095650881528854</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.002834506332874298</v>
+        <v>0.002834480255842209</v>
       </c>
       <c r="JB44" t="n">
         <v>0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.00316990539431572</v>
+        <v>0.00316983088850975</v>
       </c>
       <c r="JB45" t="n">
         <v>0.5799999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.00133957713842392</v>
+        <v>0.001339510083198547</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.3</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.0001111775636672974</v>
+        <v>0.0001111216843128204</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.5799999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.001299042254686356</v>
+        <v>-0.001299105584621429</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.8599999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.001927576959133148</v>
+        <v>-0.001927651464939117</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.002174936234951019</v>
+        <v>-0.002174902707338333</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.002069123089313507</v>
+        <v>-0.002069149166345596</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.001786321401596069</v>
+        <v>-0.001786377280950546</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.001205824315547943</v>
+        <v>-0.001205850392580032</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.0008348450064659119</v>
+        <v>-0.0008348599076271057</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.0005669891834259033</v>
+        <v>-0.0005670338869094849</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.0004634745419025421</v>
+        <v>-0.0004635490477085114</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.0004505515098571777</v>
+        <v>-0.0004505924880504608</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.0002971701323986053</v>
+        <v>-0.00029720738530159</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.0003835521638393402</v>
+        <v>0.0003835558891296387</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-8.782371878623962e-05</v>
+        <v>-8.783861994743347e-05</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.0005373135209083557</v>
+        <v>-0.0005373284220695496</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.0005051754415035248</v>
+        <v>-0.0005053281784057617</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.001210607588291168</v>
+        <v>-0.001210693269968033</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.002206366509199142</v>
+        <v>-0.002206407487392426</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.001311827450990677</v>
+        <v>-0.001311838626861572</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.0006505176424980164</v>
+        <v>-0.0006505884230136871</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.001040350645780563</v>
+        <v>-0.00104038417339325</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.002297889441251755</v>
+        <v>-0.002297908067703247</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.003112610429525375</v>
+        <v>-0.003112636506557465</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.004110444337129593</v>
+        <v>-0.00411045178771019</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.004924226552248001</v>
+        <v>-0.004924245178699493</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.005471166223287582</v>
+        <v>-0.005471173673868179</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.005590938031673431</v>
+        <v>-0.005590889602899551</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.005279053002595901</v>
+        <v>-0.005278997123241425</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.0048195980489254</v>
+        <v>-0.004819564521312714</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.004022374749183655</v>
+        <v>-0.004022378474473953</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.003694966435432434</v>
+        <v>-0.003694973886013031</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.003553267568349838</v>
+        <v>-0.003553301095962524</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.003509145230054855</v>
+        <v>-0.003509126603603363</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.003231678158044815</v>
+        <v>-0.003231685608625412</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.002952005714178085</v>
+        <v>-0.002952024340629578</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.2599999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.002529922872781754</v>
+        <v>-0.002529937773942947</v>
       </c>
       <c r="JB82" t="n">
         <v>0.02000000000000007</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.002323213964700699</v>
+        <v>-0.00232323631644249</v>
       </c>
       <c r="JB83" t="n">
         <v>0.3</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.00139886885881424</v>
+        <v>-0.001398876309394836</v>
       </c>
       <c r="JB84" t="n">
         <v>0.5799999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.0002542063593864441</v>
+        <v>0.0002542212605476379</v>
       </c>
       <c r="JB85" t="n">
         <v>0.8599999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.000657200813293457</v>
+        <v>0.0006572864949703217</v>
       </c>
       <c r="JB86" t="n">
         <v>0.9999999999999998</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.0008822642266750336</v>
+        <v>0.0008823089301586151</v>
       </c>
       <c r="JB87" t="n">
         <v>0.9999999999999998</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.003270011395215988</v>
+        <v>0.003270111978054047</v>
       </c>
       <c r="JB88" t="n">
         <v>0.7199999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.0001868419349193573</v>
+        <v>-0.0001868791878223419</v>
       </c>
       <c r="JB89" t="n">
         <v>0.4399999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.003474690020084381</v>
+        <v>-0.003474678844213486</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.4399999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.006019417196512222</v>
+        <v>-0.006019476801156998</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.7199999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.007879516109824181</v>
+        <v>-0.007879180833697319</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.9999999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.008970685303211212</v>
+        <v>-0.008970467373728752</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.9999999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.008986085653305054</v>
+        <v>-0.008985958993434906</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.9999999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.009042512625455856</v>
+        <v>-0.009042497724294662</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.9999999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.008819015696644783</v>
+        <v>-0.008819002658128738</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.9999999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.008436013013124466</v>
+        <v>-0.008436022326350212</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.9999999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.007635224610567093</v>
+        <v>-0.007635228335857391</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.9999999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.007285095751285553</v>
+        <v>-0.007284976541996002</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.7199999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.005456250160932541</v>
+        <v>-0.005456201732158661</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.1199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.003832016140222549</v>
+        <v>-0.003832124173641205</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.1199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.004830721765756607</v>
+        <v>-0.004830770194530487</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.1199999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.005906902253627777</v>
+        <v>-0.005906842648983002</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.1199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.006622299551963806</v>
+        <v>-0.006622239947319031</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.3999999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.007288359105587006</v>
+        <v>-0.007288295775651932</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.007505621761083603</v>
+        <v>-0.007505577057600021</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.007743678987026215</v>
+        <v>-0.007743638008832932</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.007695514708757401</v>
+        <v>-0.007695484906435013</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.9999999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.007014527916908264</v>
+        <v>-0.007014505565166473</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.9999999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.006223130971193314</v>
+        <v>-0.006223093718290329</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.7199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.005456633865833282</v>
+        <v>-0.005456577986478806</v>
       </c>
       <c r="JB111" t="n">
         <v>0.16</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.003996778279542923</v>
+        <v>-0.003996729850769043</v>
       </c>
       <c r="JB112" t="n">
         <v>0.4399999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.004025898873806</v>
+        <v>-0.004025869071483612</v>
       </c>
       <c r="JB113" t="n">
         <v>0.7199999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.003510620445013046</v>
+        <v>-0.003510646522045135</v>
       </c>
       <c r="JB114" t="n">
         <v>0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.003678008913993835</v>
+        <v>-0.003678079694509506</v>
       </c>
       <c r="JB115" t="n">
         <v>0.9999999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.003714520484209061</v>
+        <v>-0.003714602440595627</v>
       </c>
       <c r="JB116" t="n">
         <v>0.8599999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.00398530438542366</v>
+        <v>-0.003985341638326645</v>
       </c>
       <c r="JB117" t="n">
         <v>0.7199999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.00407332181930542</v>
+        <v>-0.004073262214660645</v>
       </c>
       <c r="JB118" t="n">
         <v>0.5799999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.004135269671678543</v>
+        <v>-0.004135262221097946</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.16</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.004242133349180222</v>
+        <v>-0.00424213707447052</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.16</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.003887441009283066</v>
+        <v>-0.003887481987476349</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.02000000000000007</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.003688827157020569</v>
+        <v>-0.003688890486955643</v>
       </c>
       <c r="JB122" t="n">
         <v>0.1199999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.003532383590936661</v>
+        <v>-0.003532413393259048</v>
       </c>
       <c r="JB123" t="n">
         <v>0.2599999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.003129877150058746</v>
+        <v>-0.003129906952381134</v>
       </c>
       <c r="JB124" t="n">
         <v>0.9999999999999998</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.002277813851833344</v>
+        <v>-0.002277843654155731</v>
       </c>
       <c r="JB125" t="n">
         <v>0.9999999999999996</v>
